--- a/02_DIA_inicio_2026_analisis_assets/rbd_9720_colegio-hernan-olguin_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9720_colegio-hernan-olguin_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42D66F64-451B-45FC-8282-EF9335BDABF4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDD4F658-045E-40DF-941B-6614C21EDBB8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63975AF3-8653-4FC0-97D9-EC32A7FF1C3D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B37517F2-C0EA-4EFB-9E7B-EC12194C924D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C1DF44E-1BAF-49D9-BB10-F651883BBDA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F29B455-8E14-458A-A463-25E1A1A81749}"/>
 </file>